--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-relatedperson.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -434,7 +434,7 @@
     <t>RelatedPerson.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -530,7 +530,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -680,7 +680,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -715,7 +715,7 @@
     <t>患者は、この人に起因する情報の解釈に影響を与えるため、患者との関係を知る必要があります。 / We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -1298,7 +1298,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1313,7 +1313,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="72.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.8203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-relatedperson.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -434,7 +434,7 @@
     <t>RelatedPerson.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -530,7 +530,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -680,7 +680,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
@@ -715,7 +715,7 @@
     <t>患者は、この人に起因する情報の解釈に影響を与えるため、患者との関係を知る必要があります。 / We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
   </si>
   <si>
     <t>code</t>
@@ -1298,7 +1298,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1313,7 +1313,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="72.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.3515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.8203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
